--- a/static/schedule.xlsx
+++ b/static/schedule.xlsx
@@ -2813,9 +2813,9 @@
           <t>黃煜森</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -2843,9 +2843,9 @@
           <t>黃煜森</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
@@ -3093,9 +3093,9 @@
           <t>黃煜森</t>
         </is>
       </c>
-      <c r="T14" s="15" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
       <c r="U14" s="14" t="inlineStr">
@@ -3213,9 +3213,9 @@
           <t>黃煜森</t>
         </is>
       </c>
-      <c r="AR14" s="15" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+      <c r="AR14" s="14" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
     </row>
@@ -3563,9 +3563,9 @@
           <t>劉錦郎</t>
         </is>
       </c>
-      <c r="Z16" s="14" t="inlineStr">
-        <is>
-          <t>洪柜峰</t>
+      <c r="Z16" s="15" t="inlineStr">
+        <is>
+          <t>羅應順</t>
         </is>
       </c>
       <c r="AA16" s="14" t="inlineStr">
@@ -3593,9 +3593,9 @@
           <t>劉錦郎</t>
         </is>
       </c>
-      <c r="AF16" s="14" t="inlineStr">
-        <is>
-          <t>洪柜峰</t>
+      <c r="AF16" s="15" t="inlineStr">
+        <is>
+          <t>羅應順</t>
         </is>
       </c>
       <c r="AG16" s="14" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>陳志偉</t>
+          <t>余金原</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>陳志偉</t>
+          <t>余金原</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
@@ -3753,9 +3753,9 @@
           <t>劉錦郎</t>
         </is>
       </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>洪柜峰</t>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>羅應順</t>
         </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
@@ -3873,9 +3873,9 @@
           <t>劉錦郎</t>
         </is>
       </c>
-      <c r="AR17" s="11" t="inlineStr">
-        <is>
-          <t>洪柜峰</t>
+      <c r="AR17" s="16" t="inlineStr">
+        <is>
+          <t>羅應順</t>
         </is>
       </c>
     </row>
@@ -3910,187 +3910,187 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
+          <t>陳志偉</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>范振宇</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>邱冠霖</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>王金誠</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>秦桔萬</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>陳志偉</t>
+        </is>
+      </c>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>林森發</t>
+        </is>
+      </c>
+      <c r="P18" s="14" t="inlineStr">
+        <is>
+          <t>周育稔</t>
+        </is>
+      </c>
+      <c r="Q18" s="14" t="inlineStr">
+        <is>
+          <t>彭偉慎</t>
+        </is>
+      </c>
+      <c r="R18" s="14" t="inlineStr">
+        <is>
+          <t>方振彬</t>
+        </is>
+      </c>
+      <c r="S18" s="14" t="inlineStr">
+        <is>
           <t>余金原</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
-        <is>
-          <t>羅應順</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>范振宇</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>邱冠霖</t>
-        </is>
-      </c>
-      <c r="K18" s="14" t="inlineStr">
-        <is>
-          <t>王金誠</t>
-        </is>
-      </c>
-      <c r="L18" s="14" t="inlineStr">
-        <is>
-          <t>秦桔萬</t>
-        </is>
-      </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>呂明峯</t>
+        </is>
+      </c>
+      <c r="U18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="V18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="X18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="Y18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="Z18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AA18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AB18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AC18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AD18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AE18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AF18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AG18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AH18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AI18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AJ18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AK18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AL18" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AM18" s="14" t="inlineStr">
+        <is>
+          <t>林森發</t>
+        </is>
+      </c>
+      <c r="AN18" s="14" t="inlineStr">
+        <is>
+          <t>周育稔</t>
+        </is>
+      </c>
+      <c r="AO18" s="14" t="inlineStr">
+        <is>
+          <t>彭偉慎</t>
+        </is>
+      </c>
+      <c r="AP18" s="14" t="inlineStr">
+        <is>
+          <t>方振彬</t>
+        </is>
+      </c>
+      <c r="AQ18" s="14" t="inlineStr">
         <is>
           <t>余金原</t>
-        </is>
-      </c>
-      <c r="N18" s="15" t="inlineStr">
-        <is>
-          <t>羅應順</t>
-        </is>
-      </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>林森發</t>
-        </is>
-      </c>
-      <c r="P18" s="14" t="inlineStr">
-        <is>
-          <t>周育稔</t>
-        </is>
-      </c>
-      <c r="Q18" s="14" t="inlineStr">
-        <is>
-          <t>彭偉慎</t>
-        </is>
-      </c>
-      <c r="R18" s="14" t="inlineStr">
-        <is>
-          <t>方振彬</t>
-        </is>
-      </c>
-      <c r="S18" s="14" t="inlineStr">
-        <is>
-          <t>陳志偉</t>
-        </is>
-      </c>
-      <c r="T18" s="14" t="inlineStr">
-        <is>
-          <t>呂明峯</t>
-        </is>
-      </c>
-      <c r="U18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="V18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="W18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="X18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="Y18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="Z18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AA18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AB18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AC18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AD18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AE18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AF18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AG18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AH18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AI18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AJ18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AK18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AL18" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AM18" s="14" t="inlineStr">
-        <is>
-          <t>林森發</t>
-        </is>
-      </c>
-      <c r="AN18" s="14" t="inlineStr">
-        <is>
-          <t>周育稔</t>
-        </is>
-      </c>
-      <c r="AO18" s="14" t="inlineStr">
-        <is>
-          <t>彭偉慎</t>
-        </is>
-      </c>
-      <c r="AP18" s="14" t="inlineStr">
-        <is>
-          <t>方振彬</t>
-        </is>
-      </c>
-      <c r="AQ18" s="14" t="inlineStr">
-        <is>
-          <t>陳志偉</t>
         </is>
       </c>
       <c r="AR18" s="14" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>余金原</t>
-        </is>
-      </c>
-      <c r="T19" s="16" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+          <t>陳志偉</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>余金原</t>
-        </is>
-      </c>
-      <c r="AR19" s="16" t="inlineStr">
-        <is>
-          <t>羅應順</t>
+          <t>陳志偉</t>
+        </is>
+      </c>
+      <c r="AR19" s="11" t="inlineStr">
+        <is>
+          <t>洪柜峰</t>
         </is>
       </c>
     </row>

--- a/static/schedule.xlsx
+++ b/static/schedule.xlsx
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>彭偉慎</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>彭偉慎</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="Q12" s="14" t="inlineStr">
         <is>
-          <t>彭偉慎</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="R12" s="14" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AO12" s="14" t="inlineStr">
         <is>
-          <t>彭偉慎</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="AP12" s="14" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>彭偉慎</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>彭偉慎</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>彭偉慎</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>彭偉慎</t>
         </is>
       </c>
       <c r="AO19" s="11" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AO24" s="14" t="inlineStr">
         <is>
-          <t>王金誠</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="AP24" s="14" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="R31" s="11" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="AO31" s="11" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>王金誠</t>
         </is>
       </c>
       <c r="AP31" s="11" t="inlineStr">

--- a/static/schedule.xlsx
+++ b/static/schedule.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="V6" s="14" t="inlineStr">
         <is>
-          <t>林宏儒</t>
+          <t>許世勳</t>
         </is>
       </c>
       <c r="W6" s="14" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AB6" s="14" t="inlineStr">
         <is>
-          <t>林宏儒</t>
+          <t>許世勳</t>
         </is>
       </c>
       <c r="AC6" s="14" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AH7" s="11" t="inlineStr">
         <is>
-          <t>林宏儒</t>
+          <t>許世勳</t>
         </is>
       </c>
       <c r="AI7" s="11" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>黃煜森</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>黃煜森</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -2150,187 +2150,187 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
+          <t>張哲維</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>呂明峯</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>黃榮國</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>孫景泰</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>王瑞發</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>張日曜</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>張哲維</t>
+        </is>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>呂明峯</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>范振宇</t>
+        </is>
+      </c>
+      <c r="P10" s="14" t="inlineStr">
+        <is>
+          <t>周育稔</t>
+        </is>
+      </c>
+      <c r="Q10" s="14" t="inlineStr">
+        <is>
+          <t>劉暐丞</t>
+        </is>
+      </c>
+      <c r="R10" s="14" t="inlineStr">
+        <is>
+          <t>方振彬</t>
+        </is>
+      </c>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
           <t>黃煜森</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>呂明峯</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>黃榮國</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>孫景泰</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>王瑞發</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>張日曜</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>林宏儒</t>
+        </is>
+      </c>
+      <c r="U10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="V10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="W10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="X10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="Y10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="Z10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AA10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AB10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AC10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AD10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AE10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AF10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AG10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AH10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AI10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AJ10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AK10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AL10" s="14" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="AM10" s="14" t="inlineStr">
+        <is>
+          <t>范振宇</t>
+        </is>
+      </c>
+      <c r="AN10" s="14" t="inlineStr">
+        <is>
+          <t>周育稔</t>
+        </is>
+      </c>
+      <c r="AO10" s="14" t="inlineStr">
+        <is>
+          <t>劉暐丞</t>
+        </is>
+      </c>
+      <c r="AP10" s="14" t="inlineStr">
+        <is>
+          <t>方振彬</t>
+        </is>
+      </c>
+      <c r="AQ10" s="14" t="inlineStr">
         <is>
           <t>黃煜森</t>
-        </is>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>呂明峯</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>范振宇</t>
-        </is>
-      </c>
-      <c r="P10" s="14" t="inlineStr">
-        <is>
-          <t>周育稔</t>
-        </is>
-      </c>
-      <c r="Q10" s="14" t="inlineStr">
-        <is>
-          <t>劉暐丞</t>
-        </is>
-      </c>
-      <c r="R10" s="14" t="inlineStr">
-        <is>
-          <t>方振彬</t>
-        </is>
-      </c>
-      <c r="S10" s="14" t="inlineStr">
-        <is>
-          <t>張哲維</t>
-        </is>
-      </c>
-      <c r="T10" s="14" t="inlineStr">
-        <is>
-          <t>林宏儒</t>
-        </is>
-      </c>
-      <c r="U10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="V10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="W10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="X10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="Y10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="Z10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AA10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AB10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AC10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AD10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AE10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AF10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AG10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AH10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AI10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AJ10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AK10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AL10" s="14" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="AM10" s="14" t="inlineStr">
-        <is>
-          <t>范振宇</t>
-        </is>
-      </c>
-      <c r="AN10" s="14" t="inlineStr">
-        <is>
-          <t>周育稔</t>
-        </is>
-      </c>
-      <c r="AO10" s="14" t="inlineStr">
-        <is>
-          <t>劉暐丞</t>
-        </is>
-      </c>
-      <c r="AP10" s="14" t="inlineStr">
-        <is>
-          <t>方振彬</t>
-        </is>
-      </c>
-      <c r="AQ10" s="14" t="inlineStr">
-        <is>
-          <t>張哲維</t>
         </is>
       </c>
       <c r="AR10" s="14" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="T11" s="11" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="AQ11" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="AR11" s="11" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Y13" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>余金原</t>
         </is>
       </c>
       <c r="Z13" s="11" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AE13" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>余金原</t>
         </is>
       </c>
       <c r="AF13" s="11" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="Y14" s="14" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>陳志偉</t>
         </is>
       </c>
       <c r="Z14" s="14" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AE14" s="14" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>陳志偉</t>
         </is>
       </c>
       <c r="AF14" s="14" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AK14" s="14" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>余金原</t>
         </is>
       </c>
       <c r="AL14" s="14" t="inlineStr">
@@ -3233,61 +3233,61 @@
           <t>林森發</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>黃榮國</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>彭偉慎</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>孫景泰</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>劉錦郎</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>羅應順</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>林森發</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>羅應順</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>彭偉慎</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>孫景泰</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>劉錦郎</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>許世勳</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>林森發</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>羅應順</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>彭偉慎</t>
-        </is>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>孫景泰</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>劉錦郎</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>許世勳</t>
-        </is>
-      </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
           <t>黃經洲</t>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>陳志偉</t>
         </is>
       </c>
       <c r="T15" s="11" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AQ15" s="11" t="inlineStr">
         <is>
-          <t>張哲維</t>
+          <t>陳志偉</t>
         </is>
       </c>
       <c r="AR15" s="11" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="Y20" s="14" t="inlineStr">
         <is>
-          <t>余金原</t>
+          <t>黃煜森</t>
         </is>
       </c>
       <c r="Z20" s="16" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AE20" s="14" t="inlineStr">
         <is>
-          <t>余金原</t>
+          <t>黃煜森</t>
         </is>
       </c>
       <c r="AF20" s="16" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AK21" s="11" t="inlineStr">
         <is>
-          <t>余金原</t>
+          <t>黃煜森</t>
         </is>
       </c>
       <c r="AL21" s="15" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>許敦智</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>許敦智</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="Z27" s="11" t="inlineStr">
         <is>
-          <t>許世勳</t>
+          <t>林宏儒</t>
         </is>
       </c>
       <c r="AA27" s="11" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="AF27" s="11" t="inlineStr">
         <is>
-          <t>許世勳</t>
+          <t>林宏儒</t>
         </is>
       </c>
       <c r="AG27" s="11" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AI27" s="11" t="inlineStr">
         <is>
-          <t>許敦智</t>
+          <t>王瑞發</t>
         </is>
       </c>
       <c r="AJ27" s="11" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="W28" s="14" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>許敦智</t>
         </is>
       </c>
       <c r="X28" s="14" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AC28" s="14" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>許敦智</t>
         </is>
       </c>
       <c r="AD28" s="14" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="AL28" s="14" t="inlineStr">
         <is>
-          <t>許世勳</t>
+          <t>林宏儒</t>
         </is>
       </c>
       <c r="AM28" s="14" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="Q29" s="11" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>許敦智</t>
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="AO29" s="11" t="inlineStr">
         <is>
-          <t>王瑞發</t>
+          <t>許敦智</t>
         </is>
       </c>
       <c r="AP29" s="11" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="S32" s="14" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="T32" s="14" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="AQ32" s="14" t="inlineStr">
         <is>
-          <t>黃煜森</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="AR32" s="14" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="Y35" s="11" t="inlineStr">
         <is>
-          <t>陳志偉</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="Z35" s="11" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AE35" s="11" t="inlineStr">
         <is>
-          <t>陳志偉</t>
+          <t>張哲維</t>
         </is>
       </c>
       <c r="AF35" s="11" t="inlineStr">
